--- a/output/archive/BrindlewytheData/Studies/2021/BW21_0453/Results/BW21_0453_hERG-CYP_RUN04.xlsx
+++ b/output/archive/BrindlewytheData/Studies/2021/BW21_0453/Results/BW21_0453_hERG-CYP_RUN04.xlsx
@@ -175,7 +175,7 @@
   <commentList>
     <comment ref="E3" authorId="0" shapeId="0">
       <text>
-        <t>Geometric mean of accepted cells; censored replicates excluded</t>
+        <t>Geometric mean of finite cell IC50s when they are the majority of accepted cells; otherwise &gt;30 µM (&gt;10 µM where precipitation limited the top concentration). n = accepted cells (finite).</t>
       </text>
     </comment>
   </commentList>
@@ -529,13 +529,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:D36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="34" customWidth="1" min="2" max="2"/>
+    <col width="44" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -552,6 +552,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
@@ -591,12 +592,12 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>Study Director</t>
+          <t>Study lead</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Dr L. Benmezroun</t>
+          <t>Dr L. Benmezroun (Study Director)</t>
         </is>
       </c>
     </row>
@@ -674,10 +675,11 @@
         <v>0.029</v>
       </c>
     </row>
+    <row r="15"/>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Study summary (benchmark)</t>
+          <t>Study summary</t>
         </is>
       </c>
     </row>
@@ -899,6 +901,7 @@
     <mergeCell ref="A2:D2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -906,28 +909,29 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H47"/>
+  <dimension ref="A1:H48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="13.5" customWidth="1" min="2" max="2"/>
-    <col width="13.5" customWidth="1" min="3" max="3"/>
-    <col width="13.5" customWidth="1" min="4" max="4"/>
-    <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="17.1" customWidth="1" min="6" max="6"/>
-    <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="48" customWidth="1" min="1" max="1"/>
+    <col width="18.8" customWidth="1" min="2" max="2"/>
+    <col width="18.8" customWidth="1" min="3" max="3"/>
+    <col width="18.8" customWidth="1" min="4" max="4"/>
+    <col width="19.85" customWidth="1" min="5" max="5"/>
+    <col width="21.95" customWidth="1" min="6" max="6"/>
+    <col width="18.8" customWidth="1" min="7" max="7"/>
+    <col width="48" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>hERG automated patch clamp: tail-current IC50, 6-point, top 30 µM</t>
-        </is>
-      </c>
-    </row>
+          <t>hERG automated patch clamp: tail-current IC50 per cell, 6-point, top 30 µM</t>
+        </is>
+      </c>
+    </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
@@ -936,22 +940,22 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>IC50 rep 1 (µM)</t>
+          <t>IC50 cell 1 (µM)</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>IC50 rep 2 (µM)</t>
+          <t>IC50 cell 2 (µM)</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>IC50 rep 3 (µM)</t>
+          <t>IC50 cell 3 (µM)</t>
         </is>
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>IC50 mean (µM)</t>
+          <t>IC50 geomean (µM)</t>
         </is>
       </c>
       <c r="F3" s="4" t="inlineStr">
@@ -961,7 +965,7 @@
       </c>
       <c r="G3" s="4" t="inlineStr">
         <is>
-          <t>n</t>
+          <t>n cells (finite)</t>
         </is>
       </c>
       <c r="H3" s="4" t="inlineStr">
@@ -995,8 +999,10 @@
       <c r="F4" s="2" t="n">
         <v>23</v>
       </c>
-      <c r="G4" s="2" t="n">
-        <v>2</v>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>2 (0)</t>
+        </is>
       </c>
       <c r="H4" s="2" t="inlineStr"/>
     </row>
@@ -1019,8 +1025,10 @@
       <c r="F5" s="2" t="n">
         <v>47</v>
       </c>
-      <c r="G5" s="2" t="n">
-        <v>2</v>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>2 (2)</t>
+        </is>
       </c>
       <c r="H5" s="2" t="inlineStr"/>
     </row>
@@ -1043,8 +1051,10 @@
       <c r="F6" s="2" t="n">
         <v>56</v>
       </c>
-      <c r="G6" s="2" t="n">
-        <v>2</v>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>2 (2)</t>
+        </is>
       </c>
       <c r="H6" s="2" t="inlineStr"/>
     </row>
@@ -1071,8 +1081,10 @@
       <c r="F7" s="2" t="n">
         <v>22</v>
       </c>
-      <c r="G7" s="2" t="n">
-        <v>2</v>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>2 (1)</t>
+        </is>
       </c>
       <c r="H7" s="2" t="inlineStr"/>
     </row>
@@ -1097,8 +1109,10 @@
       <c r="F8" s="2" t="n">
         <v>48</v>
       </c>
-      <c r="G8" s="2" t="n">
-        <v>3</v>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>3 (3)</t>
+        </is>
       </c>
       <c r="H8" s="2" t="inlineStr"/>
     </row>
@@ -1121,8 +1135,10 @@
       <c r="F9" s="2" t="n">
         <v>42</v>
       </c>
-      <c r="G9" s="2" t="n">
-        <v>2</v>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>2 (2)</t>
+        </is>
       </c>
       <c r="H9" s="2" t="inlineStr"/>
     </row>
@@ -1147,8 +1163,10 @@
       <c r="F10" s="2" t="n">
         <v>46</v>
       </c>
-      <c r="G10" s="2" t="n">
-        <v>3</v>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>3 (3)</t>
+        </is>
       </c>
       <c r="H10" s="2" t="inlineStr"/>
     </row>
@@ -1171,8 +1189,10 @@
       <c r="F11" s="2" t="n">
         <v>59</v>
       </c>
-      <c r="G11" s="2" t="n">
-        <v>2</v>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>2 (2)</t>
+        </is>
       </c>
       <c r="H11" s="2" t="inlineStr"/>
     </row>
@@ -1195,8 +1215,10 @@
       <c r="F12" s="2" t="n">
         <v>37</v>
       </c>
-      <c r="G12" s="2" t="n">
-        <v>2</v>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>2 (2)</t>
+        </is>
       </c>
       <c r="H12" s="2" t="inlineStr"/>
     </row>
@@ -1219,8 +1241,10 @@
       <c r="F13" s="2" t="n">
         <v>30</v>
       </c>
-      <c r="G13" s="2" t="n">
-        <v>2</v>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>2 (2)</t>
+        </is>
       </c>
       <c r="H13" s="2" t="inlineStr"/>
     </row>
@@ -1243,8 +1267,10 @@
       <c r="F14" s="2" t="n">
         <v>53</v>
       </c>
-      <c r="G14" s="2" t="n">
-        <v>2</v>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>2 (2)</t>
+        </is>
       </c>
       <c r="H14" s="2" t="inlineStr"/>
     </row>
@@ -1267,8 +1293,10 @@
       <c r="F15" s="2" t="n">
         <v>69</v>
       </c>
-      <c r="G15" s="2" t="n">
-        <v>2</v>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>2 (2)</t>
+        </is>
       </c>
       <c r="H15" s="2" t="inlineStr"/>
     </row>
@@ -1291,8 +1319,10 @@
       <c r="F16" s="2" t="n">
         <v>71</v>
       </c>
-      <c r="G16" s="2" t="n">
-        <v>2</v>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>2 (2)</t>
+        </is>
       </c>
       <c r="H16" s="2" t="inlineStr"/>
     </row>
@@ -1315,8 +1345,10 @@
       <c r="F17" s="2" t="n">
         <v>64</v>
       </c>
-      <c r="G17" s="2" t="n">
-        <v>2</v>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>2 (2)</t>
+        </is>
       </c>
       <c r="H17" s="2" t="inlineStr"/>
     </row>
@@ -1341,8 +1373,10 @@
       <c r="F18" s="2" t="n">
         <v>50</v>
       </c>
-      <c r="G18" s="2" t="n">
-        <v>3</v>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>3 (3)</t>
+        </is>
       </c>
       <c r="H18" s="2" t="inlineStr"/>
     </row>
@@ -1367,8 +1401,10 @@
       <c r="F19" s="2" t="n">
         <v>42</v>
       </c>
-      <c r="G19" s="2" t="n">
-        <v>3</v>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>3 (3)</t>
+        </is>
       </c>
       <c r="H19" s="2" t="inlineStr"/>
     </row>
@@ -1391,8 +1427,10 @@
       <c r="F20" s="2" t="n">
         <v>61</v>
       </c>
-      <c r="G20" s="2" t="n">
-        <v>2</v>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>2 (2)</t>
+        </is>
       </c>
       <c r="H20" s="2" t="inlineStr"/>
     </row>
@@ -1415,8 +1453,10 @@
       <c r="F21" s="2" t="n">
         <v>35</v>
       </c>
-      <c r="G21" s="2" t="n">
-        <v>2</v>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>2 (2)</t>
+        </is>
       </c>
       <c r="H21" s="2" t="inlineStr"/>
     </row>
@@ -1439,8 +1479,10 @@
       <c r="F22" s="2" t="n">
         <v>75</v>
       </c>
-      <c r="G22" s="2" t="n">
-        <v>2</v>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>2 (2)</t>
+        </is>
       </c>
       <c r="H22" s="2" t="inlineStr"/>
     </row>
@@ -1463,8 +1505,10 @@
       <c r="F23" s="2" t="n">
         <v>81</v>
       </c>
-      <c r="G23" s="2" t="n">
-        <v>2</v>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>2 (2)</t>
+        </is>
       </c>
       <c r="H23" s="2" t="inlineStr"/>
     </row>
@@ -1487,8 +1531,10 @@
       <c r="F24" s="2" t="n">
         <v>40</v>
       </c>
-      <c r="G24" s="2" t="n">
-        <v>2</v>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>2 (2)</t>
+        </is>
       </c>
       <c r="H24" s="2" t="inlineStr"/>
     </row>
@@ -1511,8 +1557,10 @@
       <c r="F25" s="2" t="n">
         <v>63</v>
       </c>
-      <c r="G25" s="2" t="n">
-        <v>2</v>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>2 (2)</t>
+        </is>
       </c>
       <c r="H25" s="2" t="inlineStr"/>
     </row>
@@ -1543,8 +1591,10 @@
       <c r="F26" s="2" t="n">
         <v>26</v>
       </c>
-      <c r="G26" s="2" t="n">
-        <v>3</v>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>3 (1)</t>
+        </is>
       </c>
       <c r="H26" s="2" t="inlineStr"/>
     </row>
@@ -1569,8 +1619,10 @@
       <c r="F27" s="2" t="n">
         <v>47</v>
       </c>
-      <c r="G27" s="2" t="n">
-        <v>3</v>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>3 (3)</t>
+        </is>
       </c>
       <c r="H27" s="2" t="inlineStr"/>
     </row>
@@ -1593,8 +1645,10 @@
       <c r="F28" s="2" t="n">
         <v>37</v>
       </c>
-      <c r="G28" s="2" t="n">
-        <v>2</v>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>2 (2)</t>
+        </is>
       </c>
       <c r="H28" s="2" t="inlineStr"/>
     </row>
@@ -1617,8 +1671,10 @@
       <c r="F29" s="2" t="n">
         <v>84</v>
       </c>
-      <c r="G29" s="2" t="n">
-        <v>2</v>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>2 (2)</t>
+        </is>
       </c>
       <c r="H29" s="2" t="inlineStr"/>
     </row>
@@ -1641,8 +1697,10 @@
       <c r="F30" s="2" t="n">
         <v>28</v>
       </c>
-      <c r="G30" s="2" t="n">
-        <v>2</v>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>2 (2)</t>
+        </is>
       </c>
       <c r="H30" s="2" t="inlineStr"/>
     </row>
@@ -1665,8 +1723,10 @@
       <c r="F31" s="2" t="n">
         <v>29</v>
       </c>
-      <c r="G31" s="2" t="n">
-        <v>2</v>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>2 (2)</t>
+        </is>
       </c>
       <c r="H31" s="2" t="inlineStr"/>
     </row>
@@ -1689,8 +1749,10 @@
       <c r="F32" s="2" t="n">
         <v>68</v>
       </c>
-      <c r="G32" s="2" t="n">
-        <v>2</v>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>2 (2)</t>
+        </is>
       </c>
       <c r="H32" s="2" t="inlineStr"/>
     </row>
@@ -1713,8 +1775,10 @@
       <c r="F33" s="2" t="n">
         <v>71</v>
       </c>
-      <c r="G33" s="2" t="n">
-        <v>2</v>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>2 (2)</t>
+        </is>
       </c>
       <c r="H33" s="2" t="inlineStr"/>
     </row>
@@ -1737,8 +1801,10 @@
       <c r="F34" s="2" t="n">
         <v>34</v>
       </c>
-      <c r="G34" s="2" t="n">
-        <v>2</v>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>2 (2)</t>
+        </is>
       </c>
       <c r="H34" s="2" t="inlineStr"/>
     </row>
@@ -1761,8 +1827,10 @@
       <c r="F35" s="2" t="n">
         <v>32</v>
       </c>
-      <c r="G35" s="2" t="n">
-        <v>2</v>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>2 (2)</t>
+        </is>
       </c>
       <c r="H35" s="2" t="inlineStr"/>
     </row>
@@ -1785,8 +1853,10 @@
       <c r="F36" s="2" t="n">
         <v>46</v>
       </c>
-      <c r="G36" s="2" t="n">
-        <v>2</v>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>2 (2)</t>
+        </is>
       </c>
       <c r="H36" s="2" t="inlineStr"/>
     </row>
@@ -1809,8 +1879,10 @@
       <c r="F37" s="2" t="n">
         <v>49</v>
       </c>
-      <c r="G37" s="2" t="n">
-        <v>2</v>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>2 (2)</t>
+        </is>
       </c>
       <c r="H37" s="2" t="inlineStr"/>
     </row>
@@ -1833,8 +1905,10 @@
       <c r="F38" s="2" t="n">
         <v>57</v>
       </c>
-      <c r="G38" s="2" t="n">
-        <v>2</v>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>2 (2)</t>
+        </is>
       </c>
       <c r="H38" s="2" t="inlineStr"/>
     </row>
@@ -1857,8 +1931,10 @@
       <c r="F39" s="2" t="n">
         <v>57</v>
       </c>
-      <c r="G39" s="2" t="n">
-        <v>2</v>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>2 (2)</t>
+        </is>
       </c>
       <c r="H39" s="2" t="inlineStr"/>
     </row>
@@ -1881,8 +1957,10 @@
       <c r="F40" s="2" t="n">
         <v>48</v>
       </c>
-      <c r="G40" s="2" t="n">
-        <v>2</v>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>2 (2)</t>
+        </is>
       </c>
       <c r="H40" s="2" t="inlineStr"/>
     </row>
@@ -1907,8 +1985,10 @@
       <c r="F41" s="2" t="n">
         <v>46</v>
       </c>
-      <c r="G41" s="2" t="n">
-        <v>3</v>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>3 (3)</t>
+        </is>
       </c>
       <c r="H41" s="2" t="inlineStr"/>
     </row>
@@ -1931,8 +2011,10 @@
       <c r="F42" s="2" t="n">
         <v>62</v>
       </c>
-      <c r="G42" s="2" t="n">
-        <v>2</v>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>2 (2)</t>
+        </is>
       </c>
       <c r="H42" s="2" t="inlineStr"/>
     </row>
@@ -1957,8 +2039,10 @@
       <c r="F43" s="2" t="n">
         <v>42</v>
       </c>
-      <c r="G43" s="2" t="n">
-        <v>3</v>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>3 (3)</t>
+        </is>
       </c>
       <c r="H43" s="2" t="inlineStr"/>
     </row>
@@ -1983,12 +2067,14 @@
       <c r="F44" s="2" t="n">
         <v>55</v>
       </c>
-      <c r="G44" s="2" t="n">
-        <v>3</v>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>3 (3)</t>
+        </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>Run 2 rejected (E-4031 outside range); repeated</t>
+          <t>First run rejected (E-4031 outside range); repeated</t>
         </is>
       </c>
     </row>
@@ -2011,11 +2097,14 @@
       <c r="F45" s="2" t="n">
         <v>41</v>
       </c>
-      <c r="G45" s="2" t="n">
-        <v>2</v>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>2 (2)</t>
+        </is>
       </c>
       <c r="H45" s="2" t="inlineStr"/>
     </row>
+    <row r="46"/>
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
         <is>
@@ -2023,8 +2112,16 @@
         </is>
       </c>
     </row>
+    <row r="48">
+      <c r="A48" s="5" t="inlineStr">
+        <is>
+          <t>Compound IC50 = geometric mean of finite cell IC50s when they are the majority of accepted cells; otherwise reported as &gt;30 µM (or &gt;10 µM where solubility-limited)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
@@ -2034,15 +2131,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:F48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="48" customWidth="1" min="1" max="1"/>
     <col width="13" customWidth="1" min="2" max="2"/>
     <col width="13" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="13.55" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="13" customWidth="1" min="6" max="6"/>
   </cols>
@@ -2054,6 +2151,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
@@ -3010,6 +3108,7 @@
         <v>35</v>
       </c>
     </row>
+    <row r="46"/>
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
         <is>
@@ -3026,6 +3125,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
@@ -3034,14 +3134,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:C45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="48" customWidth="1" min="1" max="1"/>
     <col width="13" customWidth="1" min="2" max="2"/>
-    <col width="13.5" customWidth="1" min="3" max="3"/>
+    <col width="17.75" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3100,7 +3200,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
@@ -3155,7 +3255,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>testosterone</t>
+          <t>midazolam</t>
         </is>
       </c>
     </row>
@@ -3183,7 +3283,7 @@
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
@@ -3202,7 +3302,7 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>testosterone</t>
+          <t>midazolam</t>
         </is>
       </c>
     </row>
@@ -3213,7 +3313,7 @@
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
@@ -3228,7 +3328,7 @@
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>0.83</v>
+        <v>0.71</v>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
@@ -3243,7 +3343,7 @@
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>2.7</v>
+        <v>3.7</v>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
@@ -3309,11 +3409,11 @@
         </is>
       </c>
       <c r="B17" s="2" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>testosterone</t>
+          <t>midazolam</t>
         </is>
       </c>
     </row>
@@ -3324,7 +3424,7 @@
         </is>
       </c>
       <c r="B18" s="2" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
@@ -3345,7 +3445,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>testosterone</t>
+          <t>midazolam</t>
         </is>
       </c>
     </row>
@@ -3356,7 +3456,7 @@
         </is>
       </c>
       <c r="B20" s="2" t="n">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
@@ -3371,11 +3471,11 @@
         </is>
       </c>
       <c r="B21" s="2" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>testosterone</t>
+          <t>midazolam</t>
         </is>
       </c>
     </row>
@@ -3392,7 +3492,7 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>testosterone</t>
+          <t>midazolam</t>
         </is>
       </c>
     </row>
@@ -3437,7 +3537,7 @@
         </is>
       </c>
       <c r="B25" s="2" t="n">
-        <v>4.9</v>
+        <v>4.1</v>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
@@ -3458,7 +3558,7 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>testosterone</t>
+          <t>midazolam</t>
         </is>
       </c>
     </row>
@@ -3469,11 +3569,11 @@
         </is>
       </c>
       <c r="B27" s="2" t="n">
-        <v>4.6</v>
+        <v>7.6</v>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>testosterone</t>
+          <t>midazolam</t>
         </is>
       </c>
     </row>
@@ -3490,7 +3590,7 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>testosterone</t>
+          <t>midazolam</t>
         </is>
       </c>
     </row>
@@ -3518,7 +3618,7 @@
         </is>
       </c>
       <c r="B30" s="2" t="n">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
@@ -3533,11 +3633,11 @@
         </is>
       </c>
       <c r="B31" s="2" t="n">
-        <v>11</v>
+        <v>9.6</v>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>testosterone</t>
+          <t>midazolam</t>
         </is>
       </c>
     </row>
@@ -3565,11 +3665,11 @@
         </is>
       </c>
       <c r="B33" s="2" t="n">
-        <v>7.7</v>
+        <v>6.7</v>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>testosterone</t>
+          <t>midazolam</t>
         </is>
       </c>
     </row>
@@ -3597,11 +3697,11 @@
         </is>
       </c>
       <c r="B35" s="2" t="n">
-        <v>3.5</v>
+        <v>6.3</v>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>testosterone</t>
+          <t>midazolam</t>
         </is>
       </c>
     </row>
@@ -3629,7 +3729,7 @@
         </is>
       </c>
       <c r="B37" s="2" t="n">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
@@ -3644,7 +3744,7 @@
         </is>
       </c>
       <c r="B38" s="2" t="n">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
@@ -3659,7 +3759,7 @@
         </is>
       </c>
       <c r="B39" s="2" t="n">
-        <v>1.4</v>
+        <v>1.1</v>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
@@ -3674,7 +3774,7 @@
         </is>
       </c>
       <c r="B40" s="2" t="n">
-        <v>6.7</v>
+        <v>4.8</v>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
@@ -3689,11 +3789,11 @@
         </is>
       </c>
       <c r="B41" s="2" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>testosterone</t>
+          <t>midazolam</t>
         </is>
       </c>
     </row>
@@ -3710,7 +3810,7 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>testosterone</t>
+          <t>midazolam</t>
         </is>
       </c>
     </row>
@@ -3721,7 +3821,7 @@
         </is>
       </c>
       <c r="B43" s="2" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
@@ -3729,15 +3829,17 @@
         </is>
       </c>
     </row>
+    <row r="44"/>
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
         <is>
-          <t>7-point curve, top 50 µM; ketoconazole control</t>
+          <t>7-point curve, top 50 µM; ketoconazole control run alongside on every plate</t>
         </is>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -3745,15 +3847,18 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="26" customWidth="1" min="6" max="6"/>
+    <col width="6" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3774,10 +3879,20 @@
       </c>
       <c r="D1" s="6" t="inlineStr">
         <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="E1" s="6" t="inlineStr">
+        <is>
+          <t>Historical mean</t>
+        </is>
+      </c>
+      <c r="F1" s="6" t="inlineStr">
+        <is>
           <t>Acceptance</t>
         </is>
       </c>
-      <c r="E1" s="6" t="inlineStr">
+      <c r="G1" s="6" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -3799,10 +3914,16 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
+          <t>nM</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr"/>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
           <t>5-50 nM</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="G2" s="2" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -3824,10 +3945,18 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>within 3-fold of historical mean</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
+          <t>µM</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>0.5-2 x historical mean</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -3849,10 +3978,18 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>within 3-fold of historical mean</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
+          <t>µM</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>0.5-2 x historical mean</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -3874,10 +4011,18 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>within 3-fold of historical mean</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
+          <t>µM</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>0.5-2 x historical mean</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -3899,10 +4044,18 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>within 3-fold of historical mean</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
+          <t>µM</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>0.5-2 x historical mean</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -3924,23 +4077,33 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>within 3-fold of historical mean</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
+          <t>µM</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>0.5-2 x historical mean</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
     </row>
+    <row r="8"/>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>All runs met plate acceptance criteria. Checked by Ines Alvarado.</t>
+          <t>All accepted runs met plate acceptance criteria; rejected runs were repeated as noted on the hERG sheet. Checked by Ines Alvarado.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>